--- a/examples/kns/io_list.xlsx
+++ b/examples/kns/io_list.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перечень" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$3:$AE$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$3:$AE$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE61"/>
+  <dimension ref="A1:AE62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -837,91 +837,58 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PT201</t>
+          <t>LIC101</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Давление в напорном коллекторе</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AI</t>
+          <t>Регулятор уровня в приёмном резервуаре: частота ведущего насоса</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AnalogInput</t>
+          <t>Pid</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>201</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
+        <v>104</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>бар</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5</v>
+          <t>м</t>
+        </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Коллектор</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
+          <t>Резервуар</t>
+        </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>tFilter=T#1S; astLimit[L].rHyst_eu=0.1; astLimit[LL].rHyst_eu=0.1</t>
+          <t>eAction=Direct; xUseOutAct=TRUE; rKp=2.0; rTi_s=300.0; rSpMin_eu=1.0; rSpMax_eu=3.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FT202</t>
+          <t>PT201</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Расход в напорном коллекторе</t>
+          <t>Давление в напорном коллекторе</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -935,7 +902,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -946,18 +913,32 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>м³/ч</t>
-        </is>
+          <t>бар</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>30</v>
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5</v>
       </c>
       <c r="P8" t="n">
-        <v>30</v>
+        <v>5</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -970,50 +951,59 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>tFilter=T#3S; rLowCut_pct=1.0; astLimit[L].rHyst_eu=5.0; astAlarm[L].ePriority=Medium</t>
+          <t>tFilter=T#1S; astLimit[L].rHyst_eu=0.1; astLimit[LL].rHyst_eu=0.1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LS203</t>
+          <t>FT202</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Затопление камеры задвижек</t>
+          <t>Расход в напорном коллекторе</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DigitalInput</t>
+          <t>AnalogInput</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>500</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>м³/ч</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>30</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+        <v>30</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1022,96 +1012,83 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="U9" t="n">
         <v>3</v>
       </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>tFilter=T#3S; rLowCut_pct=1.0; astLimit[L].rHyst_eu=5.0; astAlarm[L].ePriority=Medium</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P101_RUN</t>
+          <t>LS203</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Насос Н1: команда «Работа» на ПЧ</t>
+          <t>Затопление камеры задвижек</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>P101</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MotorVfd</t>
+          <t>DigitalInput</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>203</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CMD_RUN</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Насос Н1</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Насос Н1</t>
+          <t>Коллектор</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ES301</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>tMinStop=T#30S; uiMaxStartsPerHour=10; stVfd.rSpeedMin_pct=60.0; stVfd.rRampUp_pctps=5.0; stVfd.rRampDown_pctps=5.0; stVfd.xFbFromComm=FALSE; stVfd.xCommLossIsFault=FALSE</t>
-        </is>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P101_RFB</t>
+          <t>P101_RUN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Насос Н1: ПЧ в работе (релейный выход ПЧ)</t>
+          <t>Насос Н1: команда «Работа» на ПЧ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1119,10 +1096,29 @@
           <t>P101</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MotorVfd</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>11</v>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>RUN_FB</t>
-        </is>
+          <t>CMD_RUN</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Насос Н1</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>15</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1131,22 +1127,32 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="U11" t="n">
         <v>1</v>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ES301</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>tMinStop=T#30S; uiMaxStartsPerHour=10; stVfd.rSpeedMin_pct=60.0; stVfd.rRampUp_pctps=5.0; stVfd.rRampDown_pctps=5.0; stVfd.xFbFromComm=FALSE; stVfd.xCommLossIsFault=FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P101_FLT</t>
+          <t>P101_RFB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Насос Н1: авария ПЧ (релейный выход ПЧ)</t>
+          <t>Насос Н1: ПЧ в работе (релейный выход ПЧ)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1161,7 +1167,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>FAULT</t>
+          <t>RUN_FB</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1175,18 +1181,18 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HS114</t>
+          <t>P101_FLT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Насос Н1: переключатель «Местное/Дистанционное» в положении «Местное»</t>
+          <t>Насос Н1: авария ПЧ (релейный выход ПЧ)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1201,7 +1207,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LOCAL</t>
+          <t>FAULT</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1215,23 +1221,23 @@
         </is>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P101_CTW</t>
+          <t>HS114</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Насос Н1: слово управления ПЧ</t>
+          <t>Насос Н1: переключатель «Местное/Дистанционное» в положении «Местное»</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1241,7 +1247,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>VFD_CTW</t>
+          <t>LOCAL</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1249,35 +1255,24 @@
           <t>Насос Н1</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>RS485-1</t>
-        </is>
-      </c>
-      <c r="W14" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>WORD</t>
-        </is>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P101_FREF</t>
+          <t>P101_CTW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Насос Н1: задание частоты ПЧ</t>
+          <t>Насос Н1: слово управления ПЧ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1292,18 +1287,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SPEED_REF</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>50</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Гц</t>
+          <t>VFD_CTW</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1323,23 +1307,23 @@
         <v>16</v>
       </c>
       <c r="Y15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>UINT</t>
+          <t>WORD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P101_STW</t>
+          <t>P101_FREF</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Насос Н1: слово состояния ПЧ</t>
+          <t>Насос Н1: задание частоты ПЧ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1354,7 +1338,18 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>VFD_STW</t>
+          <t>SPEED_REF</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>50</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Гц</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -1371,26 +1366,26 @@
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>WORD</t>
+          <t>UINT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P101_FACT</t>
+          <t>P101_STW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Насос Н1: фактическая частота ПЧ</t>
+          <t>Насос Н1: слово состояния ПЧ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1405,18 +1400,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SPEED_ACT</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>50</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Гц</t>
+          <t>VFD_STW</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -1436,23 +1420,23 @@
         <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>UINT</t>
+          <t>WORD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT111</t>
+          <t>P101_FACT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Насос Н1: ток двигателя (измеряет ПЧ)</t>
+          <t>Насос Н1: фактическая частота ПЧ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1460,42 +1444,25 @@
           <t>MB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AnalogInput</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>111</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>P101</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>SPEED_ACT</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>А</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>34</v>
-      </c>
-      <c r="M18" t="n">
-        <v>31</v>
-      </c>
-      <c r="P18" t="n">
-        <v>10</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Гц</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -1515,28 +1482,23 @@
         <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
           <t>UINT</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>rRawLo_cnt=0.0; rRawHi_cnt=600.0; tFilter=T#1S</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P101_FCODE</t>
+          <t>IT111</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Насос Н1: код последней аварии ПЧ (читает адаптер ПЧ)</t>
+          <t>Насос Н1: ток двигателя (измеряет ПЧ)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1544,14 +1506,42 @@
           <t>MB</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>P101</t>
-        </is>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AnalogInput</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>111</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AUX</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>60</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>34</v>
+      </c>
+      <c r="M19" t="n">
+        <v>31</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -1571,46 +1561,43 @@
         <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
           <t>UINT</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>rRawLo_cnt=0.0; rRawHi_cnt=600.0; tFilter=T#1S</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TS112</t>
+          <t>P101_FCODE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Насос Н1: перегрев обмотки (термовыключатели, реле защиты насоса)</t>
+          <t>Насос Н1: код последней аварии ПЧ (читает адаптер ПЧ)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>DigitalInput</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>112</v>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>P101</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>AUX</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -1618,29 +1605,35 @@
           <t>Насос Н1</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="U20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>xInvert=TRUE</t>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>RS485-1</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>103</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>UINT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MS113</t>
+          <t>TS112</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Насос Н1: протечка в камеру статора (датчик влажности, реле защиты насоса)</t>
+          <t>Насос Н1: перегрев обмотки (термовыключатели, реле защиты насоса)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1654,19 +1647,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="P21" t="n">
-        <v>10</v>
-      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -1680,92 +1670,79 @@
         </is>
       </c>
       <c r="U21" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>xInvert=TRUE</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P102_RUN</t>
+          <t>MS113</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Насос Н2: команда «Работа» на ПЧ</t>
+          <t>Насос Н1: протечка в камеру статора (датчик влажности, реле защиты насоса)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>P102</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MotorVfd</t>
+          <t>DigitalInput</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CMD_RUN</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Насос Н2</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="P22" t="n">
         <v>10</v>
       </c>
-      <c r="Q22" t="n">
-        <v>15</v>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Насос Н2</t>
+          <t>Насос Н1</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ES301</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>tMinStop=T#30S; uiMaxStartsPerHour=10; stVfd.rSpeedMin_pct=60.0; stVfd.rRampUp_pctps=5.0; stVfd.rRampDown_pctps=5.0; stVfd.xFbFromComm=FALSE; stVfd.xCommLossIsFault=FALSE</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P102_RFB</t>
+          <t>P102_RUN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Насос Н2: ПЧ в работе (релейный выход ПЧ)</t>
+          <t>Насос Н2: команда «Работа» на ПЧ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1773,10 +1750,29 @@
           <t>P102</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MotorVfd</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>12</v>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>RUN_FB</t>
-        </is>
+          <t>CMD_RUN</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Насос Н2</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>15</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -1785,22 +1781,32 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="U23" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ES301</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>tMinStop=T#30S; uiMaxStartsPerHour=10; stVfd.rSpeedMin_pct=60.0; stVfd.rRampUp_pctps=5.0; stVfd.rRampDown_pctps=5.0; stVfd.xFbFromComm=FALSE; stVfd.xCommLossIsFault=FALSE</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P102_FLT</t>
+          <t>P102_RFB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Насос Н2: авария ПЧ (релейный выход ПЧ)</t>
+          <t>Насос Н2: ПЧ в работе (релейный выход ПЧ)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1815,7 +1821,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>FAULT</t>
+          <t>RUN_FB</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -1829,18 +1835,18 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HS124</t>
+          <t>P102_FLT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Насос Н2: переключатель «Местное/Дистанционное» в положении «Местное»</t>
+          <t>Насос Н2: авария ПЧ (релейный выход ПЧ)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1855,7 +1861,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>LOCAL</t>
+          <t>FAULT</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -1869,23 +1875,23 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P102_CTW</t>
+          <t>HS124</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Насос Н2: слово управления ПЧ</t>
+          <t>Насос Н2: переключатель «Местное/Дистанционное» в положении «Местное»</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1895,7 +1901,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>VFD_CTW</t>
+          <t>LOCAL</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -1903,35 +1909,24 @@
           <t>Насос Н2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>RS485-1</t>
-        </is>
-      </c>
-      <c r="W26" t="n">
-        <v>2</v>
-      </c>
-      <c r="X26" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>WORD</t>
-        </is>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P102_FREF</t>
+          <t>P102_CTW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Насос Н2: задание частоты ПЧ</t>
+          <t>Насос Н2: слово управления ПЧ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1946,18 +1941,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SPEED_REF</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>50</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Гц</t>
+          <t>VFD_CTW</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -1977,23 +1961,23 @@
         <v>16</v>
       </c>
       <c r="Y27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>UINT</t>
+          <t>WORD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>P102_STW</t>
+          <t>P102_FREF</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Насос Н2: слово состояния ПЧ</t>
+          <t>Насос Н2: задание частоты ПЧ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2008,7 +1992,18 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>VFD_STW</t>
+          <t>SPEED_REF</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>50</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Гц</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -2025,26 +2020,26 @@
         <v>2</v>
       </c>
       <c r="X28" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y28" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>WORD</t>
+          <t>UINT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P102_FACT</t>
+          <t>P102_STW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Насос Н2: фактическая частота ПЧ</t>
+          <t>Насос Н2: слово состояния ПЧ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2059,18 +2054,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SPEED_ACT</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>50</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Гц</t>
+          <t>VFD_STW</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -2090,23 +2074,23 @@
         <v>3</v>
       </c>
       <c r="Y29" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>UINT</t>
+          <t>WORD</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT121</t>
+          <t>P102_FACT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Насос Н2: ток двигателя (измеряет ПЧ)</t>
+          <t>Насос Н2: фактическая частота ПЧ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2114,42 +2098,25 @@
           <t>MB</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AnalogInput</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>121</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>P102</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>SPEED_ACT</t>
         </is>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>А</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>34</v>
-      </c>
-      <c r="M30" t="n">
-        <v>31</v>
-      </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Гц</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -2169,28 +2136,23 @@
         <v>3</v>
       </c>
       <c r="Y30" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
           <t>UINT</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>rRawLo_cnt=0.0; rRawHi_cnt=600.0; tFilter=T#1S</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>P102_FCODE</t>
+          <t>IT121</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Насос Н2: код последней аварии ПЧ (читает адаптер ПЧ)</t>
+          <t>Насос Н2: ток двигателя (измеряет ПЧ)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2198,14 +2160,42 @@
           <t>MB</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>P102</t>
-        </is>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AnalogInput</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>121</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>AUX</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>60</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>34</v>
+      </c>
+      <c r="M31" t="n">
+        <v>31</v>
+      </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -2225,46 +2215,43 @@
         <v>3</v>
       </c>
       <c r="Y31" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
           <t>UINT</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>rRawLo_cnt=0.0; rRawHi_cnt=600.0; tFilter=T#1S</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TS122</t>
+          <t>P102_FCODE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Насос Н2: перегрев обмотки (термовыключатели, реле защиты насоса)</t>
+          <t>Насос Н2: код последней аварии ПЧ (читает адаптер ПЧ)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>DigitalInput</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>122</v>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>P102</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>AUX</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -2272,29 +2259,35 @@
           <t>Насос Н2</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="U32" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>xInvert=TRUE</t>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>RS485-1</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>2</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>103</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>UINT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MS123</t>
+          <t>TS122</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Насос Н2: протечка в камеру статора (датчик влажности, реле защиты насоса)</t>
+          <t>Насос Н2: перегрев обмотки (термовыключатели, реле защиты насоса)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2308,19 +2301,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="P33" t="n">
-        <v>10</v>
-      </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -2334,92 +2324,79 @@
         </is>
       </c>
       <c r="U33" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>xInvert=TRUE</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>P103_RUN</t>
+          <t>MS123</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Насос Н3: команда «Работа» на ПЧ</t>
+          <t>Насос Н2: протечка в камеру статора (датчик влажности, реле защиты насоса)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>P103</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MotorVfd</t>
+          <t>DigitalInput</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CMD_RUN</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Насос Н3</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="P34" t="n">
         <v>10</v>
       </c>
-      <c r="Q34" t="n">
-        <v>15</v>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Насос Н3</t>
+          <t>Насос Н2</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="U34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>ES301</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>tMinStop=T#30S; uiMaxStartsPerHour=10; stVfd.rSpeedMin_pct=60.0; stVfd.rRampUp_pctps=5.0; stVfd.rRampDown_pctps=5.0; stVfd.xFbFromComm=FALSE; stVfd.xCommLossIsFault=FALSE</t>
-        </is>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>P103_RFB</t>
+          <t>P103_RUN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Насос Н3: ПЧ в работе (релейный выход ПЧ)</t>
+          <t>Насос Н3: команда «Работа» на ПЧ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2427,10 +2404,29 @@
           <t>P103</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>MotorVfd</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>13</v>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>RUN_FB</t>
-        </is>
+          <t>CMD_RUN</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Насос Н3</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>15</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -2439,22 +2435,32 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="U35" t="n">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>ES301</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>tMinStop=T#30S; uiMaxStartsPerHour=10; stVfd.rSpeedMin_pct=60.0; stVfd.rRampUp_pctps=5.0; stVfd.rRampDown_pctps=5.0; stVfd.xFbFromComm=FALSE; stVfd.xCommLossIsFault=FALSE</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P103_FLT</t>
+          <t>P103_RFB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Насос Н3: авария ПЧ (релейный выход ПЧ)</t>
+          <t>Насос Н3: ПЧ в работе (релейный выход ПЧ)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2469,7 +2475,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FAULT</t>
+          <t>RUN_FB</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -2483,18 +2489,18 @@
         </is>
       </c>
       <c r="U36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HS134</t>
+          <t>P103_FLT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Насос Н3: переключатель «Местное/Дистанционное» в положении «Местное»</t>
+          <t>Насос Н3: авария ПЧ (релейный выход ПЧ)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2509,7 +2515,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>LOCAL</t>
+          <t>FAULT</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -2523,23 +2529,23 @@
         </is>
       </c>
       <c r="U37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>P103_CTW</t>
+          <t>HS134</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Насос Н3: слово управления ПЧ</t>
+          <t>Насос Н3: переключатель «Местное/Дистанционное» в положении «Местное»</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2549,7 +2555,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>VFD_CTW</t>
+          <t>LOCAL</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -2557,35 +2563,24 @@
           <t>Насос Н3</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>RS485-1</t>
-        </is>
-      </c>
-      <c r="W38" t="n">
-        <v>3</v>
-      </c>
-      <c r="X38" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>WORD</t>
-        </is>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>P103_FREF</t>
+          <t>P103_CTW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Насос Н3: задание частоты ПЧ</t>
+          <t>Насос Н3: слово управления ПЧ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2600,18 +2595,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SPEED_REF</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>50</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Гц</t>
+          <t>VFD_CTW</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -2631,23 +2615,23 @@
         <v>16</v>
       </c>
       <c r="Y39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>UINT</t>
+          <t>WORD</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>P103_STW</t>
+          <t>P103_FREF</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Насос Н3: слово состояния ПЧ</t>
+          <t>Насос Н3: задание частоты ПЧ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2662,7 +2646,18 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>VFD_STW</t>
+          <t>SPEED_REF</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>50</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Гц</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -2679,26 +2674,26 @@
         <v>3</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y40" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>WORD</t>
+          <t>UINT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>P103_FACT</t>
+          <t>P103_STW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Насос Н3: фактическая частота ПЧ</t>
+          <t>Насос Н3: слово состояния ПЧ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2713,18 +2708,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SPEED_ACT</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>50</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Гц</t>
+          <t>VFD_STW</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -2744,23 +2728,23 @@
         <v>3</v>
       </c>
       <c r="Y41" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>UINT</t>
+          <t>WORD</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IT131</t>
+          <t>P103_FACT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Насос Н3: ток двигателя (измеряет ПЧ)</t>
+          <t>Насос Н3: фактическая частота ПЧ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2768,42 +2752,25 @@
           <t>MB</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AnalogInput</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>131</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>P103</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>SPEED_ACT</t>
         </is>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>А</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>34</v>
-      </c>
-      <c r="M42" t="n">
-        <v>31</v>
-      </c>
-      <c r="P42" t="n">
-        <v>10</v>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Гц</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -2823,28 +2790,23 @@
         <v>3</v>
       </c>
       <c r="Y42" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
           <t>UINT</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>rRawLo_cnt=0.0; rRawHi_cnt=600.0; tFilter=T#1S</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>P103_FCODE</t>
+          <t>IT131</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Насос Н3: код последней аварии ПЧ (читает адаптер ПЧ)</t>
+          <t>Насос Н3: ток двигателя (измеряет ПЧ)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2852,14 +2814,42 @@
           <t>MB</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>P103</t>
-        </is>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AnalogInput</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>131</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AUX</t>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>60</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>34</v>
+      </c>
+      <c r="M43" t="n">
+        <v>31</v>
+      </c>
+      <c r="P43" t="n">
+        <v>10</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -2879,46 +2869,43 @@
         <v>3</v>
       </c>
       <c r="Y43" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
           <t>UINT</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>rRawLo_cnt=0.0; rRawHi_cnt=600.0; tFilter=T#1S</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TS132</t>
+          <t>P103_FCODE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Насос Н3: перегрев обмотки (термовыключатели, реле защиты насоса)</t>
+          <t>Насос Н3: код последней аварии ПЧ (читает адаптер ПЧ)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>DigitalInput</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>132</v>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>P103</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>AUX</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -2926,29 +2913,35 @@
           <t>Насос Н3</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="U44" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>xInvert=TRUE</t>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>RS485-1</t>
+        </is>
+      </c>
+      <c r="W44" t="n">
+        <v>3</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>103</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>UINT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MS133</t>
+          <t>TS132</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Насос Н3: протечка в камеру статора (датчик влажности, реле защиты насоса)</t>
+          <t>Насос Н3: перегрев обмотки (термовыключатели, реле защиты насоса)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2962,19 +2955,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="P45" t="n">
-        <v>10</v>
-      </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -2988,18 +2978,23 @@
         </is>
       </c>
       <c r="U45" t="n">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>xInvert=TRUE</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ES301</t>
+          <t>MS133</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Напряжение на вводе в норме (реле контроля фаз)</t>
+          <t>Насос Н3: протечка в камеру статора (датчик влажности, реле защиты насоса)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3013,7 +3008,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>301</v>
+        <v>133</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3021,41 +3016,36 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Электроснабжение</t>
+          <t>Насос Н3</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="U46" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>xAlarmOnTrue=FALSE</t>
-        </is>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>YS302</t>
+          <t>ES301</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ИБП шкафа управления: работа от батарей</t>
+          <t>Напряжение на вводе в норме (реле контроля фаз)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3069,7 +3059,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3077,11 +3067,11 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -3095,18 +3085,23 @@
         </is>
       </c>
       <c r="U47" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>xAlarmOnTrue=FALSE</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>YS303</t>
+          <t>YS302</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ИБП шкафа управления: неисправность или разряд батарей</t>
+          <t>ИБП шкафа управления: работа от батарей</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3120,7 +3115,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3146,91 +3141,69 @@
         </is>
       </c>
       <c r="U48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AT401</t>
+          <t>YS303</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Концентрация сероводорода H₂S в павильоне</t>
+          <t>ИБП шкафа управления: неисправность или разряд батарей</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AnalogInput</t>
+          <t>DigitalInput</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>401</v>
+        <v>303</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>40</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>мг/м³</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>10</v>
-      </c>
-      <c r="M49" t="n">
-        <v>5</v>
+          <t>IN</t>
+        </is>
       </c>
       <c r="P49" t="n">
         <v>5</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Павильон</t>
+          <t>Электроснабжение</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="U49" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>astLimit[HH].rHyst_eu=0.5; astLimit[H].rHyst_eu=0.5</t>
-        </is>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AT402</t>
+          <t>AT401</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Концентрация метана CH₄ в павильоне</t>
+          <t>Концентрация сероводорода H₂S в павильоне</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3244,7 +3217,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3255,18 +3228,18 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>% НКПР</t>
+          <t>мг/м³</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P50" t="n">
         <v>5</v>
@@ -3287,28 +3260,28 @@
         </is>
       </c>
       <c r="U50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>astLimit[HH].rHyst_eu=1.0; astLimit[H].rHyst_eu=1.0</t>
+          <t>astLimit[HH].rHyst_eu=0.5; astLimit[H].rHyst_eu=0.5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TT403</t>
+          <t>AT402</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Температура воздуха в павильоне</t>
+          <t>Концентрация метана CH₄ в павильоне</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3317,7 +3290,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3325,28 +3298,28 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>°C</t>
-        </is>
+          <t>% НКПР</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>20</v>
       </c>
       <c r="M51" t="n">
-        <v>35</v>
-      </c>
-      <c r="N51" t="n">
+        <v>10</v>
+      </c>
+      <c r="P51" t="n">
         <v>5</v>
       </c>
-      <c r="P51" t="n">
-        <v>60</v>
-      </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -3354,67 +3327,68 @@
           <t>Павильон</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>RS485-2</t>
-        </is>
-      </c>
-      <c r="W51" t="n">
-        <v>10</v>
-      </c>
-      <c r="X51" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>REAL</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>5</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>astLimit[H].rHyst_eu=1.0; astLimit[L].rHyst_eu=1.0</t>
+          <t>astLimit[HH].rHyst_eu=1.0; astLimit[H].rHyst_eu=1.0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ZS404</t>
+          <t>TT403</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Дверь павильона открыта</t>
+          <t>Температура воздуха в павильоне</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DigitalInput</t>
+          <t>AnalogInput</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>-40</v>
+      </c>
+      <c r="J52" t="n">
+        <v>60</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>35</v>
+      </c>
+      <c r="N52" t="n">
+        <v>5</v>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -3426,24 +3400,45 @@
           <t>Павильон</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="U52" t="n">
-        <v>7</v>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>RS485-2</t>
+        </is>
+      </c>
+      <c r="W52" t="n">
+        <v>10</v>
+      </c>
+      <c r="X52" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>astLimit[H].rHyst_eu=1.0; astLimit[L].rHyst_eu=1.0</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>YS405</t>
+          <t>ZS404</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Пожар (сигнал прибора пожарной сигнализации)</t>
+          <t>Дверь павильона открыта</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3457,16 +3452,19 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
+      <c r="P53" t="n">
+        <v>2</v>
+      </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -3480,57 +3478,41 @@
         </is>
       </c>
       <c r="U53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>V1_RUN</t>
+          <t>YS405</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Вентилятор В1: команда «Работа»</t>
+          <t>Пожар (сигнал прибора пожарной сигнализации)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>V1</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Motor</t>
+          <t>DigitalInput</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>14</v>
+        <v>405</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CMD_RUN</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Вытяжной вентилятор В1 павильона</t>
-        </is>
-      </c>
-      <c r="P54" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>5</v>
+          <t>IN</t>
+        </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -3540,37 +3522,27 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="U54" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>ES301</t>
-        </is>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>tMinStop=T#10S</t>
-        </is>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>V1_RFB</t>
+          <t>V1_RUN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Вентилятор В1: в работе (блок-контакт пускателя)</t>
+          <t>Вентилятор В1: команда «Работа»</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3578,9 +3550,33 @@
           <t>V1</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>14</v>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>RUN_FB</t>
+          <t>CMD_RUN</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Вытяжной вентилятор В1 павильона</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>5</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -3590,22 +3586,32 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="U55" t="n">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>ES301</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>tMinStop=T#10S</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V1_FLT</t>
+          <t>V1_RFB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Вентилятор В1: авария (автомат защиты двигателя)</t>
+          <t>Вентилятор В1: в работе (блок-контакт пускателя)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3620,7 +3626,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>FAULT</t>
+          <t>RUN_FB</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -3634,18 +3640,18 @@
         </is>
       </c>
       <c r="U56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HS501</t>
+          <t>V1_FLT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Кнопка «Сброс аварий» на двери шкафа управления</t>
+          <t>Вентилятор В1: авария (автомат защиты двигателя)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3653,22 +3659,19 @@
           <t>DI</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>DigitalInput</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>501</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>FAULT</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Шкаф управления</t>
+          <t>Павильон</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -3677,18 +3680,18 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HS502</t>
+          <t>HS501</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Кнопка «Отключить звук» на двери шкафа управления</t>
+          <t>Кнопка «Сброс аварий» на двери шкафа управления</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3702,7 +3705,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3720,28 +3723,36 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HA1</t>
+          <t>HS502</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Сирена на шкафу управления</t>
+          <t>Кнопка «Отключить звук» на двери шкафа управления</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DO</t>
-        </is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DigitalInput</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>502</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>AUX</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -3751,22 +3762,22 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="U59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HL1</t>
+          <t>HA1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Лампа «Авария» на двери шкафа управления</t>
+          <t>Сирена на шкафу управления</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3790,46 +3801,81 @@
         </is>
       </c>
       <c r="U60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>HL1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Лампа «Авария» на двери шкафа управления</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Шкаф управления</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>K1</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Реле «Общая авария» (сухой контакт в диспетчерскую)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>AUX</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>Шкаф управления</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="U61" t="n">
+      <c r="U62" t="n">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AE61"/>
+  <autoFilter ref="A3:AE62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>